--- a/backend/src/test/resources/import/nhan-vien-co-loi.xlsx
+++ b/backend/src/test/resources/import/nhan-vien-co-loi.xlsx
@@ -540,7 +540,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0212345678</t>
+          <t>1212345678</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
